--- a/Result/profitability/6209.xlsx
+++ b/Result/profitability/6209.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.145</v>
+        <v>0.28125</v>
       </c>
       <c r="N2" t="n">
-        <v>15.6425</v>
+        <v>17.6125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.39</v>
       </c>
       <c r="M3" t="n">
-        <v>0.23875</v>
+        <v>0.3575</v>
       </c>
       <c r="N3" t="n">
-        <v>15.25875</v>
+        <v>17.55875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2575</v>
+        <v>0.3475</v>
       </c>
       <c r="N4" t="n">
-        <v>14.72625</v>
+        <v>16.515</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.22</v>
+        <v>0.29875</v>
       </c>
       <c r="N5" t="n">
-        <v>14.24</v>
+        <v>14.85625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1225</v>
+        <v>0.16625</v>
       </c>
       <c r="N6" t="n">
-        <v>11.28375</v>
+        <v>11.53375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.98</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1725</v>
+        <v>-0.135</v>
       </c>
       <c r="N7" t="n">
-        <v>8.305</v>
+        <v>8.866250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.225</v>
+        <v>-0.235</v>
       </c>
       <c r="N8" t="n">
-        <v>6.67875</v>
+        <v>5.989999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.71</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0175</v>
+        <v>-0.01750000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>8.998750000000001</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6209</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D75" t="n">
+        <v>937</v>
+      </c>
+      <c r="E75" t="n">
+        <v>319</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>137</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>38</v>
+      </c>
+      <c r="J75" t="n">
+        <v>175</v>
+      </c>
+      <c r="K75" t="n">
+        <v>131</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.6225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.09876543209876554</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.509999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1781441965729065</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.930000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2406051732552466</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
